--- a/output/Driver_Weekly_Load_Strict.xlsx
+++ b/output/Driver_Weekly_Load_Strict.xlsx
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3031.65</v>
+        <v>2581.23</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>505.27</v>
+        <v>516.25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2858.84</v>
+        <v>2588.21</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>476.47</v>
+        <v>517.64</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2835.61</v>
+        <v>2925.05</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>472.6</v>
+        <v>487.51</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2799.73</v>
+        <v>2807.34</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>466.62</v>
+        <v>467.89</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2729.91</v>
+        <v>2756.99</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>454.98</v>
+        <v>459.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2492.22</v>
+        <v>2928.62</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>415.37</v>
+        <v>488.1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2860.52</v>
+        <v>2563.25</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>476.75</v>
+        <v>427.21</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3085.61</v>
+        <v>2325.83</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>514.27</v>
+        <v>387.64</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2600.64</v>
+        <v>2600.88</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>520.13</v>
+        <v>520.1799999999999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2686.6</v>
+        <v>3074.99</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>447.77</v>
+        <v>512.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2596.19</v>
+        <v>3070.65</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>519.24</v>
+        <v>511.78</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2562.6</v>
+        <v>2891.06</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>427.1</v>
+        <v>481.84</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>

--- a/output/Driver_Weekly_Load_Strict.xlsx
+++ b/output/Driver_Weekly_Load_Strict.xlsx
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2581.23</v>
+        <v>3071.72</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>516.25</v>
+        <v>511.95</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2588.21</v>
+        <v>2562.22</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>517.64</v>
+        <v>512.4400000000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2925.05</v>
+        <v>3037.01</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>487.51</v>
+        <v>506.17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2807.34</v>
+        <v>3018.29</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>467.89</v>
+        <v>503.05</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2756.99</v>
+        <v>2535.61</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>459.5</v>
+        <v>422.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2928.62</v>
+        <v>2561.77</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>488.1</v>
+        <v>512.35</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2563.25</v>
+        <v>2612.24</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>427.21</v>
+        <v>435.37</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2325.83</v>
+        <v>2880.17</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>387.64</v>
+        <v>480.03</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2600.88</v>
+        <v>2588.95</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>520.1799999999999</v>
+        <v>431.49</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3074.99</v>
+        <v>2553.53</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>512.5</v>
+        <v>510.71</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3070.65</v>
+        <v>3063.85</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>511.78</v>
+        <v>510.64</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2891.06</v>
+        <v>2622.77</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>481.84</v>
+        <v>437.13</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>

--- a/output/Driver_Weekly_Load_Strict.xlsx
+++ b/output/Driver_Weekly_Load_Strict.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,32 +429,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>driver</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>driver_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>weekly_total_min</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>used_days</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>avg_per_used_day_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>depot</t>
         </is>
